--- a/astro-site/public/dl/kit-tareas-pasteleria/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/06-eventos-festivos.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Navidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Semana Santa" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Día Madre-Padre" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana Santa" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Día Madre-Padre" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Navidad'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Semana Santa'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Día Madre-Padre'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +98,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -126,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,54 +159,104 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -557,13 +618,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -571,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -599,8 +662,24 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -609,18 +688,18 @@
   <sheetPr>
     <tabColor rgb="00C62828"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,10 +716,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -680,18 +760,16 @@
           <t xml:space="preserve">  Planificación (Noviembre)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -717,10 +795,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -746,10 +822,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -775,10 +849,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -804,10 +876,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -833,10 +903,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -861,24 +929,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción Navideña (Diciembre)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="17" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -904,10 +971,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -933,10 +998,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -962,10 +1025,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -991,10 +1052,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1020,10 +1079,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1048,28 +1105,27 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="15" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Día de Reyes (5-6 Enero)</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Hornear roscones la madrugada del 5 al 6</t>
+          <t>Hornear roscones: 1ª hornada la madrugada del 4 al 5 (60-70 % del volumen, venta de la tarde del 5) y 2ª hornada del 5 al 6</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -1084,17 +1140,15 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>05-06 Ene</t>
+          <t>04-06 Ene</t>
         </is>
       </c>
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1120,10 +1174,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="25" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1149,10 +1201,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="25" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1178,10 +1228,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="25" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1206,6 +1254,8 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="15" t="n"/>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
@@ -1214,7 +1264,7 @@
       </c>
       <c r="D29" s="19">
         <f>COUNTIF(F5:F27,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
@@ -1225,6 +1275,7 @@
         <v>17</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
@@ -1232,13 +1283,17 @@
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
       <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-    </row>
+      <c r="G31" s="24" t="n"/>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
@@ -1249,20 +1304,29 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1271,18 +1335,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1299,10 +1363,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1342,18 +1407,16 @@
           <t xml:space="preserve">  Planificación (2 semanas antes)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1379,10 +1442,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1408,10 +1469,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1437,10 +1496,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1465,24 +1522,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción (12-14 Feb)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1508,10 +1564,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1537,10 +1591,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1566,10 +1618,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1595,10 +1645,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1624,10 +1672,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1652,6 +1698,8 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
@@ -1660,7 +1708,7 @@
       </c>
       <c r="D20" s="19">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
@@ -1671,6 +1719,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
@@ -1678,13 +1727,17 @@
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="24" t="n"/>
       <c r="E22" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-    </row>
+      <c r="G22" s="24" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
@@ -1703,11 +1756,20 @@
     <mergeCell ref="F22:G22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1716,18 +1778,18 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1744,10 +1806,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1787,18 +1850,16 @@
           <t xml:space="preserve">  Planificación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1824,10 +1885,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1853,10 +1912,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1881,28 +1938,27 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Elaborar torrijas (remojo, fritura, almíbar/canela)</t>
+          <t>Elaborar torrijas a diario (remojo, fritura, almíbar/canela) — pico Jueves y Viernes Santo</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -1917,21 +1973,19 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Jue-Vie Santo</t>
+          <t>V. Dolores → D. Resurrección</t>
         </is>
       </c>
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Elaborar monas de Pascua (bizcocho + decoración chocolate)</t>
+          <t>Elaborar y montar monas de Pascua (bizcocho + decoración chocolate) para recogida el Domingo de Resurrección y el Lunes de Pascua</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -1946,17 +2000,15 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Lun-Mié</t>
+          <t>Jue-Sáb Santo</t>
         </is>
       </c>
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1975,17 +2027,15 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Lun-Mié</t>
+          <t>Jue-Sáb Santo</t>
         </is>
       </c>
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2011,10 +2061,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2039,6 +2087,8 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
@@ -2047,7 +2097,7 @@
       </c>
       <c r="D18" s="19">
         <f>COUNTIF(F5:F16,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
@@ -2058,6 +2108,7 @@
         <v>8</v>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
@@ -2065,13 +2116,17 @@
         </is>
       </c>
       <c r="B20" s="15" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="24" t="n"/>
       <c r="E20" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-    </row>
+      <c r="G20" s="24" t="n"/>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
@@ -2090,11 +2145,20 @@
     <mergeCell ref="A10:G10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F11 F12 F13 F14 F15" type="list">
+    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2103,18 +2167,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2131,10 +2195,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2174,18 +2239,16 @@
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2211,10 +2274,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2240,10 +2301,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2268,24 +2327,23 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción y Venta</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2311,10 +2369,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2340,10 +2396,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2369,10 +2423,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2397,6 +2449,8 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
@@ -2405,7 +2459,7 @@
       </c>
       <c r="D17" s="19">
         <f>COUNTIF(F5:F15,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
@@ -2416,6 +2470,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -2423,13 +2478,17 @@
         </is>
       </c>
       <c r="B19" s="15" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="24" t="n"/>
       <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-    </row>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
@@ -2448,10 +2507,19 @@
     <mergeCell ref="A17:C17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/06-eventos-festivos.xlsx
@@ -12,12 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana Santa" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Día Madre-Padre" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comuniones (Abr-Jun)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todos los Santos (Oct-Nov)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Navidad'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Semana Santa'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Día Madre-Padre'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Comuniones (Abr-Jun)'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Todos los Santos (Oct-Nov)'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -256,6 +260,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -651,7 +665,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>▸ Navidad, Reyes, San Valentín, Día de la Madre... cada una requiere planificación</t>
+          <t>▸ Navidad, Reyes, San Valentín, Semana Santa, Día de la Madre, Comuniones y Todos los Santos: cada campaña tiene su hoja</t>
         </is>
       </c>
     </row>
@@ -666,14 +680,15 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -690,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -745,7 +760,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -929,46 +944,40 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Fijar y comunicar el horario del 24, 25 y 31 Dic y del 1 y 6 Ene</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>20 Nov</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción Navideña (Diciembre)</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="24" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Producción de turrones artesanos (2-3 semanas antes)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>1-15 Dic</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
@@ -976,10 +985,10 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Producción de polvorones y mantecados</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
+          <t>Producción de turrones artesanos (2-3 semanas antes)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1003,10 +1012,10 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Preparar masas de roscón de Reyes (fermentación 24-48h)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
+          <t>Producción de polvorones y mantecados</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1018,7 +1027,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3 Ene</t>
+          <t>1-15 Dic</t>
         </is>
       </c>
       <c r="F16" s="14" t="n"/>
@@ -1033,7 +1042,7 @@
           <t>Producción de troncos de Navidad (bûche de Noël)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1060,7 +1069,7 @@
           <t>Preparar cestas y lotes navideños</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1084,10 +1093,10 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Control de pedidos de clientes (lista de encargos)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
+          <t>Control de pedidos de clientes (lista de encargos) → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1107,17 +1116,11 @@
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Día de Reyes (5-6 Enero)</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="24" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Recogidas y Nochevieja (22-31 Dic)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="n">
@@ -1125,22 +1128,22 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Hornear roscones: 1ª hornada la madrugada del 4 al 5 (60-70 % del volumen, venta de la tarde del 5) y 2ª hornada del 5 al 6</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Cerrar los encargos de Nochebuena y Navidad y repartir las franjas de recogida → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Pastelero</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>04-06 Ene</t>
+          <t>20 Dic</t>
         </is>
       </c>
       <c r="F22" s="14" t="n"/>
@@ -1152,22 +1155,22 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Rellenar con nata, trufa, crema, cabello de ángel</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Organizar la recogida de encargos por franjas horarias (22-24 Dic)</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Pastelero</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>06 Ene</t>
+          <t>22-24 Dic</t>
         </is>
       </c>
       <c r="F23" s="14" t="n"/>
@@ -1179,22 +1182,22 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Decorar con fruta confitada, azúcar, corona</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Reforzar el despacho en los picos del 23 y 24 (turno doble)</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Pastelero</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>06 Ene</t>
+          <t>23-24 Dic</t>
         </is>
       </c>
       <c r="F24" s="14" t="n"/>
@@ -1206,22 +1209,22 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Introducir sorpresa y haba</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Cerrar los encargos de Nochevieja (postres y bandejas de dulces)</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Ayudante</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>06 Ene</t>
+          <t>29 Dic</t>
         </is>
       </c>
       <c r="F25" s="14" t="n"/>
@@ -1233,88 +1236,393 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Gestionar colas y pedidos (reforzar despacho)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
+          <t>Producir y entregar los encargos del 31 de diciembre</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Dependiente</t>
+          <t>Pastelero</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>06 Ene</t>
+          <t>31 Dic</t>
         </is>
       </c>
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27"/>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reyes (2-6 Ene)</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Cerrar los encargos de roscón y repartir las franjas de recogida → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>2 Ene</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Preparar masas de roscón de Reyes (fermentación 24-48h)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>3 Ene</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Hornear la 1ª hornada de roscones la madrugada del 4 al 5 (60-70 % del volumen, para la venta de la tarde del 5)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>04-05 Ene</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Hornear la 2ª hornada la madrugada del 5 al 6 y rellenar al momento</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>05-06 Ene</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Rellenar con nata, trufa, crema, cabello de ángel</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>05-06 Ene</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Decorar con fruta confitada, azúcar, corona</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>05-06 Ene</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Introducir sorpresa y haba</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Ayudante</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>05-06 Ene</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Control de colas y turnos de recogida (reforzar despacho)</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>05-06 Ene</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="15" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>7 Ene</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="15" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D29" s="19">
-        <f>COUNTIF(F5:F27,"✓")</f>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="12">
+        <f>COUNTIF(F5:F43,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F29" s="19" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="F45" s="14">
+        <f>COUNTIF(B5:B43,"?*")</f>
+        <v>26.0</v>
+      </c>
+      <c r="G45" s="15" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="24" t="n"/>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="24" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G43">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F35 F36 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1337,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1700,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1524,17 +1832,11 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción (12-14 Feb)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n">
@@ -1545,7 +1847,7 @@
           <t>Producción de bombones y trufas artesanas</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1572,7 +1874,7 @@
           <t>Producción de tartas individuales con forma de corazón</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1599,7 +1901,7 @@
           <t>Producción de macarons con sabores especiales (rosa, frambuesa, pasión)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1626,7 +1928,7 @@
           <t>Montar cajas regalo con selección de piezas</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1650,10 +1952,10 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Preparar tartas de encargo personalizadas</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
+          <t>Preparar tartas de encargo personalizadas → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1680,7 +1982,7 @@
           <t>Reforzar despacho para pico de ventas (14 Feb tarde)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -1699,65 +2001,145 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>15 Feb</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D20" s="19">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="12">
+        <f>COUNTIF(F5:F24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="F26" s="14">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>11.0</v>
+      </c>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="24" t="n"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="24" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1780,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1795,7 +2177,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Semana Santa</t>
+          <t>Semana Santa (Cuaresma y Pascua)</t>
         </is>
       </c>
     </row>
@@ -1835,7 +2217,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1938,46 +2320,40 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Cerrar los encargos de mona de Pascua → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Dom Ramos</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="24" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Elaborar torrijas a diario (remojo, fritura, almíbar/canela) — pico Jueves y Viernes Santo</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>V. Dolores → D. Resurrección</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n">
@@ -1985,10 +2361,10 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Elaborar y montar monas de Pascua (bizcocho + decoración chocolate) para recogida el Domingo de Resurrección y el Lunes de Pascua</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
+          <t>Elaborar torrijas a diario (remojo, fritura, almíbar/canela) — pico Jueves y Viernes Santo</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -2000,7 +2376,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Jue-Sáb Santo</t>
+          <t>V. Dolores → D. Resurrección</t>
         </is>
       </c>
       <c r="F12" s="14" t="n"/>
@@ -2012,10 +2388,10 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Producir huevos de chocolate rellenos</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
+          <t>Elaborar pestiños y leche frita (fritura, almíbar y canela)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
@@ -2027,7 +2403,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Jue-Sáb Santo</t>
+          <t>Mié-Vie Santo</t>
         </is>
       </c>
       <c r="F13" s="14" t="n"/>
@@ -2039,22 +2415,22 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Montar escaparate temático de Semana Santa</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
+          <t>Freír buñuelos de Cuaresma y rellenarlos al momento</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Dependiente</t>
+          <t>Pastelero</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Dom Ramos</t>
+          <t>Vie Santo</t>
         </is>
       </c>
       <c r="F14" s="14" t="n"/>
@@ -2066,87 +2442,284 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Gestionar pedidos de encargo (monas, huevos personalizados)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
+          <t>Elaborar y montar monas de Pascua (bizcocho + decoración chocolate) para recogida el Domingo de Resurrección y el Lunes de Pascua</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Dependiente</t>
+          <t>Pastelero</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Continuo</t>
+          <t>Jue-Sáb Santo</t>
         </is>
       </c>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Producir huevos de chocolate rellenos</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Jue-Sáb Santo</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Hornear hornazo para el Lunes de Pascua (según la zona)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Sáb Santo</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="15" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Venta y Encargos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Montar escaparate temático de Semana Santa</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Dom Ramos</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Gestionar pedidos de encargo (monas, huevos personalizados) → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Continuo</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Mar tras Pascua</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D18" s="19">
-        <f>COUNTIF(F5:F16,"✓")</f>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="12">
+        <f>COUNTIF(F5:F28,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F18" s="19" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="F30" s="14">
+        <f>COUNTIF(B5:B28,"?*")</f>
+        <v>13.0</v>
+      </c>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="24" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="24" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B20:D20"/>
+  <mergeCells count="9">
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F20 F21 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2169,7 +2742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2184,7 +2757,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Día de la Madre / Día del Padre</t>
+          <t>Día del Padre (19 de marzo) y Día de la Madre (primer domingo de mayo — fecha de este año: ____/____/________)</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2797,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2252,7 +2825,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Diseñar tartas especiales para la ocasión</t>
+          <t>Anotar la fecha de este año del Día de la Madre (primer domingo de mayo)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2262,12 +2835,12 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Jefe Pastelero</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>2 sem antes</t>
+          <t>3 sem antes</t>
         </is>
       </c>
       <c r="F6" s="14" t="n"/>
@@ -2279,7 +2852,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Abrir pedidos de tartas personalizadas (mensaje, dedicatoria)</t>
+          <t>Diseñar tartas especiales para la ocasión</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2289,7 +2862,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Jefe Pastelero</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2306,7 +2879,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Preparar packaging especial</t>
+          <t>Abrir pedidos de tartas personalizadas (mensaje, dedicatoria)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -2321,25 +2894,482 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>1 sem antes</t>
+          <t>2 sem antes</t>
         </is>
       </c>
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
     </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Preparar packaging especial</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>1 sem antes</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Producción y Venta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Producción extra de tartas (incremento 80-120%)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Día antes</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Preparar tartas con dedicatoria personalizada</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Reforzar despacho (turno doble si es necesario)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Ofrecer servicio de entrega a domicilio (si aplica)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Día siguiente</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="12">
+        <f>COUNTIF(F5:F22,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24" s="14">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>9.0</v>
+      </c>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="24" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="F26:G26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001976D2"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Comuniones (Abril-Junio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Hora Límite</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Captación y Visita (Enero-Marzo)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Preparar el catálogo de comuniones (tartas por pisos, mesas dulces, detalles) con fotos y precios</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Jefe Pastelero</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Publicar el catálogo y abrir la agenda de visitas</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Visita con la familia: fecha, nº de invitados, lugar, estilo y presupuesto orientativo</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Feb-Mar</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="15" t="n"/>
+    </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Producción y Venta</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="24" t="n"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Presupuesto, Prueba y Señal</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
@@ -2347,22 +3377,22 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Producción extra de tartas (incremento 80-120%)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Enviar el presupuesto por escrito detallando qué incluye y qué no (transporte, montaje, alquiler de soportes)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Pastelero</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Día antes</t>
+          <t>48 h tras la visita</t>
         </is>
       </c>
       <c r="F11" s="14" t="n"/>
@@ -2374,22 +3404,22 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Preparar tartas con dedicatoria personalizada</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
+          <t>Prueba de sabores con la familia (2-3 combinaciones)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Pastelero</t>
+          <t>Jefe Pastelero</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Día</t>
+          <t>4-6 sem antes</t>
         </is>
       </c>
       <c r="F12" s="14" t="n"/>
@@ -2401,22 +3431,22 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Reforzar despacho (turno doble si es necesario)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Cerrar la ficha de encargo: sabores por piso, raciones, alérgenos, dedicatoria y hora de entrega → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Dependiente</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Día</t>
+          <t>4 sem antes</t>
         </is>
       </c>
       <c r="F13" s="14" t="n"/>
@@ -2428,12 +3458,12 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Ofrecer servicio de entrega a domicilio (si aplica)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Cobrar la señal (30-50 %) y anotar el importe pendiente → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2443,72 +3473,1020 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Día</t>
+          <t>Al confirmar</t>
         </is>
       </c>
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Confirmar con la familia el nº definitivo de invitados y la hora</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>7 días antes</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Producción y Montaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Elaborar bizcochos y rellenos, y calar las plantillas de cada piso</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>2 días antes</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Montar los pisos con estructura interna y revisar el aplomo de la pieza</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Jefe Pastelero</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Día antes</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Decorar y guardar la tarta montada en cámara sin olores</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Día antes</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Preparar la mesa dulce: piezas, soportes, cartelería y etiquetas de alérgenos → 12 Control de Alérgenos de Vitrina</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Ayudante</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Día antes</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transporte y Entrega</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Preparar el transporte: caja rígida, base antideslizante, vehículo refrigerado y ruta con margen</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Día de la entrega</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Salir del obrador con 60 min de margen sobre la hora acordada</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Día de la entrega</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Montaje in situ, retoque final y foto de la pieza terminada</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Jefe Pastelero</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Día de la entrega</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Firmar la entrega con la familia y cobrar el pendiente → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Día de la entrega</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D17" s="19">
-        <f>COUNTIF(F5:F15,"✓")</f>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="12">
+        <f>COUNTIF(F5:F34,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F36" s="14">
+        <f>COUNTIF(B5:B34,"?*")</f>
+        <v>17.0</v>
+      </c>
+      <c r="G36" s="15" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="24" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A29:G29"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006D4C41"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Todos los Santos (Octubre-Noviembre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Hora Límite</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Planificación (Octubre)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Definir la colección de temporada (huesos de santo, panellets, buñuelos de viento)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Jefe Pastelero</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>10 Oct</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Pedir mazapán, almendra molida, piñones y boniato con antelación</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>12 Oct</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Publicar la colección en RRSS y abrir los encargos</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>20 Oct</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Calcular la producción por día del 28 Oct al 2 Nov</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>20 Oct</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Producción (28 Oct - 2 Nov)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Elaborar la masa de mazapán y formar los huesos de santo (yema, cabello de ángel, chocolate)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>28-31 Oct</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Elaborar panellets (piñón, almendra, coco, café)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>28-31 Oct</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="18"/>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Freír los buñuelos de viento y rellenarlos al momento (crema, nata, chocolate)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>31 Oct-1 Nov</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Etiquetar la vitrina de temporada: almendra, piñones y huevo están en casi todas las piezas → 12 Control de Alérgenos de Vitrina</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>31 Oct</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Montar el escaparate de temporada y el cartel de precios por peso</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Encargos y Venta (30 Oct - 2 Nov)</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Cerrar los encargos de bandejas y surtidos → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Organizar las recogidas del 1 de noviembre por franjas horarias</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>31 Oct</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Reforzar el despacho el 1 de noviembre (turno doble)</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>1 Nov</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Reponer la vitrina cada 2 h: el buñuelo se vende recién relleno</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>1-2 Nov</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre de Campaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Post-campaña: contar el sobrante, anotar las mermas y registrar qué se vendió y qué no → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>3 Nov</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="12">
+        <f>COUNTIF(F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="14">
+        <f>COUNTIF(B5:B29,"?*")</f>
+        <v>14.0</v>
+      </c>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="24" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="24" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F19:G19"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
